--- a/gte/nodes/LPC/compresor_blade_self_frequency.xlsx
+++ b/gte/nodes/LPC/compresor_blade_self_frequency.xlsx
@@ -552,58 +552,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>237.51742458243683</v>
+        <v>214.86010448113086</v>
       </c>
       <c r="C3">
-        <v>1488.6037267646193</v>
+        <v>1346.6024769590629</v>
       </c>
       <c r="D3">
-        <v>4168.5528325963523</v>
+        <v>3770.9052239908606</v>
       </c>
       <c r="E3">
-        <v>8174.8219376284042</v>
+        <v>7395.0073293416772</v>
       </c>
       <c r="F3">
-        <v>13508.02172132767</v>
+        <v>12219.461218393746</v>
       </c>
       <c r="G3">
-        <v>20173.460750915216</v>
+        <v>18249.069062228908</v>
       </c>
       <c r="H3">
-        <v>692.33429251100711</v>
+        <v>692.55800939732887</v>
       </c>
       <c r="I3">
-        <v>2077.0028775330215</v>
+        <v>2077.6740281919865</v>
       </c>
       <c r="J3">
-        <v>3461.6714625550358</v>
+        <v>3462.790046986644</v>
       </c>
       <c r="K3">
-        <v>4846.3400475770495</v>
+        <v>4847.9060657813015</v>
       </c>
       <c r="L3">
-        <v>6231.0086325990651</v>
+        <v>6233.0220845759595</v>
       </c>
       <c r="M3">
-        <v>7615.6772176210779</v>
+        <v>7618.1381033706166</v>
       </c>
       <c r="N3">
-        <v>1384.6685850220142</v>
+        <v>1385.1160187946578</v>
       </c>
       <c r="O3">
-        <v>2769.3371700440284</v>
+        <v>2770.2320375893155</v>
       </c>
       <c r="P3">
-        <v>4154.0057550660431</v>
+        <v>4155.348056383973</v>
       </c>
       <c r="Q3">
-        <v>5538.6743400880569</v>
+        <v>5540.464075178631</v>
       </c>
       <c r="R3">
-        <v>6923.3429251100715</v>
+        <v>6925.5800939732881</v>
       </c>
       <c r="S3">
-        <v>8308.0115101320862</v>
+        <v>8310.696112767946</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -611,58 +611,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>250.0746491741788</v>
+        <v>252.91814942654335</v>
       </c>
       <c r="C4">
-        <v>1567.3041899325315</v>
+        <v>1585.1253880200718</v>
       </c>
       <c r="D4">
-        <v>4388.93857580437</v>
+        <v>4438.8434661606088</v>
       </c>
       <c r="E4">
-        <v>8607.0137031326249</v>
+        <v>8704.880662929565</v>
       </c>
       <c r="F4">
-        <v>14222.172537180628</v>
+        <v>14383.88725449481</v>
       </c>
       <c r="G4">
-        <v>21240.004301929563</v>
+        <v>21481.516017700062</v>
       </c>
       <c r="H4">
-        <v>700.16414400353563</v>
+        <v>700.137708567517</v>
       </c>
       <c r="I4">
-        <v>2100.492432010607</v>
+        <v>2100.4131257025515</v>
       </c>
       <c r="J4">
-        <v>3500.820720017678</v>
+        <v>3500.6885428375854</v>
       </c>
       <c r="K4">
-        <v>4901.1490080247495</v>
+        <v>4900.96395997262</v>
       </c>
       <c r="L4">
-        <v>6301.4772960318214</v>
+        <v>6301.2393771076549</v>
       </c>
       <c r="M4">
-        <v>7701.8055840388924</v>
+        <v>7701.5147942426884</v>
       </c>
       <c r="N4">
-        <v>1400.3282880070713</v>
+        <v>1400.2754171350341</v>
       </c>
       <c r="O4">
-        <v>2800.6565760141425</v>
+        <v>2800.5508342700682</v>
       </c>
       <c r="P4">
-        <v>4200.984864021214</v>
+        <v>4200.826251405103</v>
       </c>
       <c r="Q4">
-        <v>5601.313152028285</v>
+        <v>5601.1016685401364</v>
       </c>
       <c r="R4">
-        <v>7001.641440035356</v>
+        <v>7001.3770856751707</v>
       </c>
       <c r="S4">
-        <v>8401.969728042428</v>
+        <v>8401.652502810206</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -670,58 +670,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>255.05651077174773</v>
+        <v>246.44845808364241</v>
       </c>
       <c r="C5">
-        <v>1598.5272370559342</v>
+        <v>1544.5775980590177</v>
       </c>
       <c r="D5">
-        <v>4476.3728064114857</v>
+        <v>4325.2970591090561</v>
       </c>
       <c r="E5">
-        <v>8778.4783085173985</v>
+        <v>8482.2082639987857</v>
       </c>
       <c r="F5">
-        <v>14505.499517468144</v>
+        <v>14015.9448547158</v>
       </c>
       <c r="G5">
-        <v>21663.137002958694</v>
+        <v>20932.015009064591</v>
       </c>
       <c r="H5">
-        <v>674.80458025073858</v>
+        <v>674.87443733867553</v>
       </c>
       <c r="I5">
-        <v>2024.413740752216</v>
+        <v>2024.6233120160266</v>
       </c>
       <c r="J5">
-        <v>3374.0229012536929</v>
+        <v>3374.3721866933774</v>
       </c>
       <c r="K5">
-        <v>4723.632061755171</v>
+        <v>4724.121061370729</v>
       </c>
       <c r="L5">
-        <v>6073.2412222566481</v>
+        <v>6073.86993604808</v>
       </c>
       <c r="M5">
-        <v>7422.8503827581253</v>
+        <v>7423.6188107254311</v>
       </c>
       <c r="N5">
-        <v>1349.6091605014772</v>
+        <v>1349.7488746773511</v>
       </c>
       <c r="O5">
-        <v>2699.2183210029543</v>
+        <v>2699.4977493547021</v>
       </c>
       <c r="P5">
-        <v>4048.8274815044319</v>
+        <v>4049.2466240320532</v>
       </c>
       <c r="Q5">
-        <v>5398.4366420059087</v>
+        <v>5398.9954987094043</v>
       </c>
       <c r="R5">
-        <v>6748.0458025073858</v>
+        <v>6748.7443733867549</v>
       </c>
       <c r="S5">
-        <v>8097.6549630088639</v>
+        <v>8098.4932480641064</v>
       </c>
     </row>
   </sheetData>
